--- a/templates/000_pm_suite/02_프로젝트 개발/08_유지보수/03_하자처리/프로젝트명_하자보수내역서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/08_유지보수/03_하자처리/프로젝트명_하자보수내역서_V1.0_20230530.xlsx
@@ -520,7 +520,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-69] SyncGuard AI 오픈 안정화 및 무상 하자보수 처리 내역 대장 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-69] SyncFlow AI 오픈 안정화 및 무상 하자보수 처리 내역 대장 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>럭셔리마케팅팀 이수현</t>
+          <t>핵심모듈구매조달팀 이수현</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>규제심의팀 김지수</t>
+          <t>규제검증팀 김지수</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>심의 결과 PDF 리포트 출력 시 긴 영문 원료명 줄바꿈 어긋남</t>
+          <t>검증 결과 PDF 리포트 출력 시 긴 영문 원소재명 줄바꿈 어긋남</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>더마화장품팀 박소연</t>
+          <t>정밀전장전장부품팀 박소연</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>'피부과 테스트 완료(무자극)' 문구에서 괄호 내 하이픈 인식 예외</t>
+          <t>'미공인기관 테스트 완료(무결함)' 조항에서 괄호 내 하이픈 인식 예외</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>BO 토큰 정산 화면에서 브랜드별 월간 CSV 내보내기 시 UTF-8 BOM 추가 요청</t>
+          <t>BO 토큰 정산 화면에서 사업부별 월간 CSV 내보내기 시 UTF-8 BOM 추가 요청</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀 윤서연</t>
+          <t>규제검증팀 윤서연</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
